--- a/meta_ads_data.xlsx
+++ b/meta_ads_data.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -479,177 +479,97 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Impressions</t>
+          <t>Clicks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20500000</v>
+        <v>263900</v>
       </c>
       <c r="C3" t="n">
-        <v>23900000</v>
+        <v>305700</v>
       </c>
       <c r="D3" t="n">
-        <v>-14.2</v>
+        <v>-13.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Reach</t>
+          <t>Conversions</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5400000</v>
+        <v>2700</v>
       </c>
       <c r="C4" t="n">
-        <v>6700000</v>
+        <v>3546</v>
       </c>
       <c r="D4" t="n">
-        <v>-19.2</v>
+        <v>-23.8</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>CRM Leads</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14.6</v>
+        <v>3100</v>
       </c>
       <c r="C5" t="n">
-        <v>13.8</v>
+        <v>4600</v>
       </c>
       <c r="D5" t="n">
-        <v>6.1</v>
+        <v>-32.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Clicks</t>
+          <t>Appointments</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>263900</v>
+        <v>480</v>
       </c>
       <c r="C6" t="n">
-        <v>305700</v>
+        <v>390</v>
       </c>
       <c r="D6" t="n">
-        <v>-13.7</v>
+        <v>23.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>Customers</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3100</v>
+        <v>210</v>
       </c>
       <c r="C7" t="n">
-        <v>4600</v>
+        <v>175</v>
       </c>
       <c r="D7" t="n">
-        <v>-32.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Purchases</t>
+          <t>Sales Amount ($)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2700</v>
+        <v>560000</v>
       </c>
       <c r="C8" t="n">
-        <v>3546</v>
+        <v>430000</v>
       </c>
       <c r="D8" t="n">
-        <v>-23.8</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>ROAS</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>5</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="D9" t="n">
-        <v>26.9</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CPM ($)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="C10" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.9</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CPC ($)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="C11" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="D11" t="n">
-        <v>2.4</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CTR (%)</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="C12" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.8</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Conversion Rate (%)</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="C13" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="D13" t="n">
-        <v>-32</v>
+        <v>30.2</v>
       </c>
     </row>
   </sheetData>
@@ -711,12 +631,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>CRM Leads</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Purchases</t>
+          <t>Conversions</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -945,7 +865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -953,10 +873,12 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -987,22 +909,32 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>CRM Leads</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Purchases</t>
+          <t>Conversions</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Appointments</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Customers</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Sales Amount ($)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>ROAS</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Frequency</t>
         </is>
       </c>
     </row>
@@ -1031,10 +963,16 @@
         <v>67</v>
       </c>
       <c r="H2" t="n">
-        <v>6.81</v>
+        <v>13</v>
       </c>
       <c r="I2" t="n">
-        <v>16.1</v>
+        <v>14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23850.68</v>
+      </c>
+      <c r="K2" t="n">
+        <v>5.95</v>
       </c>
     </row>
     <row r="3">
@@ -1044,28 +982,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4316.71</v>
+        <v>3803.84</v>
       </c>
       <c r="C3" t="n">
-        <v>545580</v>
+        <v>516663</v>
       </c>
       <c r="D3" t="n">
-        <v>217397</v>
+        <v>143905</v>
       </c>
       <c r="E3" t="n">
-        <v>9456</v>
+        <v>6767</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>87</v>
       </c>
       <c r="G3" t="n">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="H3" t="n">
-        <v>3.92</v>
+        <v>26</v>
       </c>
       <c r="I3" t="n">
-        <v>13.4</v>
+        <v>13</v>
+      </c>
+      <c r="J3" t="n">
+        <v>12424.58</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.39</v>
       </c>
     </row>
     <row r="4">
@@ -1075,28 +1019,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3823.43</v>
+        <v>3904.8</v>
       </c>
       <c r="C4" t="n">
-        <v>794254</v>
+        <v>785706</v>
       </c>
       <c r="D4" t="n">
-        <v>166062</v>
+        <v>194987</v>
       </c>
       <c r="E4" t="n">
-        <v>11865</v>
+        <v>7805</v>
       </c>
       <c r="F4" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="G4" t="n">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="H4" t="n">
-        <v>5.39</v>
+        <v>10</v>
       </c>
       <c r="I4" t="n">
-        <v>14.7</v>
+        <v>6</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23170.23</v>
+      </c>
+      <c r="K4" t="n">
+        <v>5.03</v>
       </c>
     </row>
     <row r="5">
@@ -1106,28 +1056,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3272.92</v>
+        <v>3064.32</v>
       </c>
       <c r="C5" t="n">
-        <v>503407</v>
+        <v>676472</v>
       </c>
       <c r="D5" t="n">
-        <v>160926</v>
+        <v>153396</v>
       </c>
       <c r="E5" t="n">
-        <v>11719</v>
+        <v>6759</v>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="G5" t="n">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="H5" t="n">
-        <v>4.75</v>
+        <v>21</v>
       </c>
       <c r="I5" t="n">
-        <v>13.3</v>
+        <v>9</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21659.62</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.13</v>
       </c>
     </row>
     <row r="6">
@@ -1137,28 +1093,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4097.94</v>
+        <v>4040.54</v>
       </c>
       <c r="C6" t="n">
-        <v>553587</v>
+        <v>781137</v>
       </c>
       <c r="D6" t="n">
-        <v>152156</v>
+        <v>156361</v>
       </c>
       <c r="E6" t="n">
-        <v>9112</v>
+        <v>9100</v>
       </c>
       <c r="F6" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="H6" t="n">
-        <v>7.31</v>
+        <v>19</v>
       </c>
       <c r="I6" t="n">
-        <v>15.6</v>
+        <v>14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21896.32</v>
+      </c>
+      <c r="K6" t="n">
+        <v>7.38</v>
       </c>
     </row>
     <row r="7">
@@ -1168,28 +1130,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4172.12</v>
+        <v>3781.5</v>
       </c>
       <c r="C7" t="n">
-        <v>882589</v>
+        <v>869398</v>
       </c>
       <c r="D7" t="n">
-        <v>200217</v>
+        <v>149116</v>
       </c>
       <c r="E7" t="n">
-        <v>10392</v>
+        <v>6375</v>
       </c>
       <c r="F7" t="n">
-        <v>75</v>
+        <v>144</v>
       </c>
       <c r="G7" t="n">
-        <v>98</v>
+        <v>79</v>
       </c>
       <c r="H7" t="n">
-        <v>3.85</v>
+        <v>19</v>
       </c>
       <c r="I7" t="n">
-        <v>13.8</v>
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>25685.08</v>
+      </c>
+      <c r="K7" t="n">
+        <v>7.4</v>
       </c>
     </row>
     <row r="8">
@@ -1199,28 +1167,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3868.69</v>
+        <v>3446.21</v>
       </c>
       <c r="C8" t="n">
-        <v>689600</v>
+        <v>737717</v>
       </c>
       <c r="D8" t="n">
-        <v>215674</v>
+        <v>187819</v>
       </c>
       <c r="E8" t="n">
-        <v>7575</v>
+        <v>7332</v>
       </c>
       <c r="F8" t="n">
-        <v>150</v>
+        <v>107</v>
       </c>
       <c r="G8" t="n">
-        <v>58</v>
+        <v>95</v>
       </c>
       <c r="H8" t="n">
-        <v>3.71</v>
+        <v>16</v>
       </c>
       <c r="I8" t="n">
-        <v>13.4</v>
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>16271.65</v>
+      </c>
+      <c r="K8" t="n">
+        <v>7.71</v>
       </c>
     </row>
     <row r="9">
@@ -1230,28 +1204,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3291.96</v>
+        <v>3901.66</v>
       </c>
       <c r="C9" t="n">
-        <v>541833</v>
+        <v>819360</v>
       </c>
       <c r="D9" t="n">
-        <v>170512</v>
+        <v>162431</v>
       </c>
       <c r="E9" t="n">
-        <v>6827</v>
+        <v>10375</v>
       </c>
       <c r="F9" t="n">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="G9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="H9" t="n">
-        <v>5.54</v>
+        <v>24</v>
       </c>
       <c r="I9" t="n">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="J9" t="n">
+        <v>16319.17</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.66</v>
       </c>
     </row>
     <row r="10">
@@ -1261,28 +1241,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3076.51</v>
+        <v>3969.88</v>
       </c>
       <c r="C10" t="n">
-        <v>686264</v>
+        <v>615141</v>
       </c>
       <c r="D10" t="n">
-        <v>167460</v>
+        <v>182504</v>
       </c>
       <c r="E10" t="n">
-        <v>11490</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="n">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="G10" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="H10" t="n">
-        <v>6.24</v>
+        <v>20</v>
       </c>
       <c r="I10" t="n">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="J10" t="n">
+        <v>16283.85</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.45</v>
       </c>
     </row>
     <row r="11">
@@ -1292,28 +1278,34 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>4039.52</v>
+        <v>4402.95</v>
       </c>
       <c r="C11" t="n">
-        <v>585669</v>
+        <v>876393</v>
       </c>
       <c r="D11" t="n">
-        <v>200589</v>
+        <v>181245</v>
       </c>
       <c r="E11" t="n">
-        <v>9108</v>
+        <v>7741</v>
       </c>
       <c r="F11" t="n">
-        <v>94</v>
+        <v>143</v>
       </c>
       <c r="G11" t="n">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H11" t="n">
-        <v>6.58</v>
+        <v>22</v>
       </c>
       <c r="I11" t="n">
-        <v>17.1</v>
+        <v>14</v>
+      </c>
+      <c r="J11" t="n">
+        <v>19341.63</v>
+      </c>
+      <c r="K11" t="n">
+        <v>4.69</v>
       </c>
     </row>
     <row r="12">
@@ -1323,28 +1315,34 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4119.2</v>
+        <v>3219.27</v>
       </c>
       <c r="C12" t="n">
-        <v>620087</v>
+        <v>794318</v>
       </c>
       <c r="D12" t="n">
-        <v>144207</v>
+        <v>210644</v>
       </c>
       <c r="E12" t="n">
-        <v>8584</v>
+        <v>8152</v>
       </c>
       <c r="F12" t="n">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="G12" t="n">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>3.8</v>
+        <v>28</v>
       </c>
       <c r="I12" t="n">
-        <v>17.5</v>
+        <v>10</v>
+      </c>
+      <c r="J12" t="n">
+        <v>17791.94</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.99</v>
       </c>
     </row>
     <row r="13">
@@ -1354,28 +1352,34 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3764.21</v>
+        <v>3035.16</v>
       </c>
       <c r="C13" t="n">
-        <v>876393</v>
+        <v>758744</v>
       </c>
       <c r="D13" t="n">
-        <v>181245</v>
+        <v>151915</v>
       </c>
       <c r="E13" t="n">
-        <v>7741</v>
+        <v>6385</v>
       </c>
       <c r="F13" t="n">
-        <v>143</v>
+        <v>74</v>
       </c>
       <c r="G13" t="n">
-        <v>113</v>
+        <v>69</v>
       </c>
       <c r="H13" t="n">
-        <v>5.28</v>
+        <v>30</v>
       </c>
       <c r="I13" t="n">
-        <v>17.5</v>
+        <v>6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>24673.27</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.4</v>
       </c>
     </row>
     <row r="14">
@@ -1385,28 +1389,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3580.05</v>
+        <v>2908</v>
       </c>
       <c r="C14" t="n">
-        <v>638873</v>
+        <v>700078</v>
       </c>
       <c r="D14" t="n">
-        <v>158301</v>
+        <v>218104</v>
       </c>
       <c r="E14" t="n">
-        <v>8020</v>
+        <v>9834</v>
       </c>
       <c r="F14" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="G14" t="n">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="H14" t="n">
-        <v>4.68</v>
+        <v>27</v>
       </c>
       <c r="I14" t="n">
-        <v>15.5</v>
+        <v>4</v>
+      </c>
+      <c r="J14" t="n">
+        <v>22884.53</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.02</v>
       </c>
     </row>
     <row r="15">
@@ -1416,28 +1426,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>4326.3</v>
+        <v>4304.14</v>
       </c>
       <c r="C15" t="n">
-        <v>709400</v>
+        <v>893676</v>
       </c>
       <c r="D15" t="n">
-        <v>187447</v>
+        <v>174973</v>
       </c>
       <c r="E15" t="n">
-        <v>7796</v>
+        <v>11250</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="G15" t="n">
-        <v>115</v>
+        <v>64</v>
       </c>
       <c r="H15" t="n">
-        <v>5.72</v>
+        <v>19</v>
       </c>
       <c r="I15" t="n">
-        <v>16.5</v>
+        <v>10</v>
+      </c>
+      <c r="J15" t="n">
+        <v>14530.52</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.51</v>
       </c>
     </row>
     <row r="16">
@@ -1447,28 +1463,34 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4263.87</v>
+        <v>4027.56</v>
       </c>
       <c r="C16" t="n">
-        <v>580132</v>
+        <v>877319</v>
       </c>
       <c r="D16" t="n">
-        <v>160969</v>
+        <v>174522</v>
       </c>
       <c r="E16" t="n">
-        <v>11574</v>
+        <v>10100</v>
       </c>
       <c r="F16" t="n">
+        <v>82</v>
+      </c>
+      <c r="G16" t="n">
         <v>114</v>
       </c>
-      <c r="G16" t="n">
-        <v>58</v>
-      </c>
       <c r="H16" t="n">
-        <v>5.23</v>
+        <v>13</v>
       </c>
       <c r="I16" t="n">
-        <v>15.6</v>
+        <v>14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>16775.12</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6.38</v>
       </c>
     </row>
     <row r="17">
@@ -1478,28 +1500,34 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3595.68</v>
+        <v>3835.25</v>
       </c>
       <c r="C17" t="n">
-        <v>631813</v>
+        <v>580131</v>
       </c>
       <c r="D17" t="n">
-        <v>212512</v>
+        <v>189009</v>
       </c>
       <c r="E17" t="n">
-        <v>6094</v>
+        <v>7323</v>
       </c>
       <c r="F17" t="n">
-        <v>147</v>
+        <v>129</v>
       </c>
       <c r="G17" t="n">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H17" t="n">
-        <v>6.57</v>
+        <v>10</v>
       </c>
       <c r="I17" t="n">
-        <v>15.2</v>
+        <v>13</v>
+      </c>
+      <c r="J17" t="n">
+        <v>17186.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.59</v>
       </c>
     </row>
     <row r="18">
@@ -1509,28 +1537,34 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3253.6</v>
+        <v>4379.47</v>
       </c>
       <c r="C18" t="n">
-        <v>836048</v>
+        <v>661225</v>
       </c>
       <c r="D18" t="n">
-        <v>184587</v>
+        <v>171385</v>
       </c>
       <c r="E18" t="n">
-        <v>6913</v>
+        <v>6474</v>
       </c>
       <c r="F18" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="G18" t="n">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="H18" t="n">
-        <v>4.21</v>
+        <v>12</v>
       </c>
       <c r="I18" t="n">
-        <v>12</v>
+        <v>15</v>
+      </c>
+      <c r="J18" t="n">
+        <v>19775.85</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.81</v>
       </c>
     </row>
     <row r="19">
@@ -1540,28 +1574,34 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4027.56</v>
+        <v>4093.02</v>
       </c>
       <c r="C19" t="n">
-        <v>877319</v>
+        <v>565934</v>
       </c>
       <c r="D19" t="n">
-        <v>174522</v>
+        <v>156828</v>
       </c>
       <c r="E19" t="n">
-        <v>10100</v>
+        <v>11404</v>
       </c>
       <c r="F19" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="H19" t="n">
-        <v>7.61</v>
+        <v>15</v>
       </c>
       <c r="I19" t="n">
-        <v>17.2</v>
+        <v>8</v>
+      </c>
+      <c r="J19" t="n">
+        <v>20442.78</v>
+      </c>
+      <c r="K19" t="n">
+        <v>6.23</v>
       </c>
     </row>
     <row r="20">
@@ -1571,28 +1611,34 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3307.36</v>
+        <v>4439.42</v>
       </c>
       <c r="C20" t="n">
-        <v>834993</v>
+        <v>782746</v>
       </c>
       <c r="D20" t="n">
-        <v>206540</v>
+        <v>166365</v>
       </c>
       <c r="E20" t="n">
-        <v>10988</v>
+        <v>11840</v>
       </c>
       <c r="F20" t="n">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="G20" t="n">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="H20" t="n">
-        <v>5.18</v>
+        <v>30</v>
       </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="J20" t="n">
+        <v>19009.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>5.83</v>
       </c>
     </row>
     <row r="21">
@@ -1602,28 +1648,34 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4420.95</v>
+        <v>3005.71</v>
       </c>
       <c r="C21" t="n">
-        <v>778058</v>
+        <v>617806</v>
       </c>
       <c r="D21" t="n">
-        <v>140074</v>
+        <v>148392</v>
       </c>
       <c r="E21" t="n">
-        <v>10906</v>
+        <v>8769</v>
       </c>
       <c r="F21" t="n">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="G21" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="H21" t="n">
-        <v>3.59</v>
+        <v>17</v>
       </c>
       <c r="I21" t="n">
-        <v>17.6</v>
+        <v>13</v>
+      </c>
+      <c r="J21" t="n">
+        <v>15523.48</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.82</v>
       </c>
     </row>
     <row r="22">
@@ -1633,28 +1685,34 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4293.83</v>
+        <v>3872.88</v>
       </c>
       <c r="C22" t="n">
-        <v>661225</v>
+        <v>620031</v>
       </c>
       <c r="D22" t="n">
-        <v>171385</v>
+        <v>148834</v>
       </c>
       <c r="E22" t="n">
-        <v>6474</v>
+        <v>6257</v>
       </c>
       <c r="F22" t="n">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="G22" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H22" t="n">
-        <v>3.89</v>
+        <v>26</v>
       </c>
       <c r="I22" t="n">
-        <v>14.9</v>
+        <v>7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>16455.64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5.68</v>
       </c>
     </row>
     <row r="23">
@@ -1664,28 +1722,34 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2917.66</v>
+        <v>3716.7</v>
       </c>
       <c r="C23" t="n">
-        <v>898774</v>
+        <v>879245</v>
       </c>
       <c r="D23" t="n">
-        <v>209822</v>
+        <v>214847</v>
       </c>
       <c r="E23" t="n">
-        <v>7030</v>
+        <v>10720</v>
       </c>
       <c r="F23" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G23" t="n">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="H23" t="n">
-        <v>7.76</v>
+        <v>25</v>
       </c>
       <c r="I23" t="n">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="J23" t="n">
+        <v>15046.56</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.94</v>
       </c>
     </row>
     <row r="24">
@@ -1695,28 +1759,34 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3697.05</v>
+        <v>3532.79</v>
       </c>
       <c r="C24" t="n">
-        <v>818029</v>
+        <v>722077</v>
       </c>
       <c r="D24" t="n">
-        <v>195461</v>
+        <v>193883</v>
       </c>
       <c r="E24" t="n">
-        <v>7735</v>
+        <v>9825</v>
       </c>
       <c r="F24" t="n">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="G24" t="n">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="H24" t="n">
-        <v>6.71</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>14.4</v>
+        <v>10</v>
+      </c>
+      <c r="J24" t="n">
+        <v>23651.42</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7.1</v>
       </c>
     </row>
     <row r="25">
@@ -1726,28 +1796,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3941.87</v>
+        <v>2985.76</v>
       </c>
       <c r="C25" t="n">
-        <v>695779</v>
+        <v>600448</v>
       </c>
       <c r="D25" t="n">
-        <v>197422</v>
+        <v>164931</v>
       </c>
       <c r="E25" t="n">
-        <v>10239</v>
+        <v>10393</v>
       </c>
       <c r="F25" t="n">
         <v>117</v>
       </c>
       <c r="G25" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H25" t="n">
+        <v>23</v>
+      </c>
+      <c r="I25" t="n">
+        <v>6</v>
+      </c>
+      <c r="J25" t="n">
+        <v>16456.72</v>
+      </c>
+      <c r="K25" t="n">
         <v>4.62</v>
-      </c>
-      <c r="I25" t="n">
-        <v>12.4</v>
       </c>
     </row>
     <row r="26">
@@ -1757,28 +1833,34 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2835.76</v>
+        <v>4369.55</v>
       </c>
       <c r="C26" t="n">
-        <v>790414</v>
+        <v>732328</v>
       </c>
       <c r="D26" t="n">
-        <v>170161</v>
+        <v>212132</v>
       </c>
       <c r="E26" t="n">
-        <v>10820</v>
+        <v>6802</v>
       </c>
       <c r="F26" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="G26" t="n">
-        <v>50</v>
+        <v>119</v>
       </c>
       <c r="H26" t="n">
-        <v>3.82</v>
+        <v>10</v>
       </c>
       <c r="I26" t="n">
-        <v>15.8</v>
+        <v>5</v>
+      </c>
+      <c r="J26" t="n">
+        <v>26821.87</v>
+      </c>
+      <c r="K26" t="n">
+        <v>7.32</v>
       </c>
     </row>
     <row r="27">
@@ -1788,28 +1870,34 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3189.2</v>
+        <v>3082.73</v>
       </c>
       <c r="C27" t="n">
-        <v>516469</v>
+        <v>754615</v>
       </c>
       <c r="D27" t="n">
-        <v>183309</v>
+        <v>203092</v>
       </c>
       <c r="E27" t="n">
-        <v>6580</v>
+        <v>7751</v>
       </c>
       <c r="F27" t="n">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="G27" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="H27" t="n">
-        <v>4.75</v>
+        <v>15</v>
       </c>
       <c r="I27" t="n">
-        <v>14.9</v>
+        <v>10</v>
+      </c>
+      <c r="J27" t="n">
+        <v>12034.49</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.26</v>
       </c>
     </row>
     <row r="28">
@@ -1819,28 +1907,34 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3716.7</v>
+        <v>4375.08</v>
       </c>
       <c r="C28" t="n">
-        <v>879245</v>
+        <v>738555</v>
       </c>
       <c r="D28" t="n">
-        <v>214847</v>
+        <v>177388</v>
       </c>
       <c r="E28" t="n">
-        <v>10720</v>
+        <v>9465</v>
       </c>
       <c r="F28" t="n">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c r="G28" t="n">
-        <v>81</v>
+        <v>112</v>
       </c>
       <c r="H28" t="n">
-        <v>7.03</v>
+        <v>14</v>
       </c>
       <c r="I28" t="n">
-        <v>16.8</v>
+        <v>7</v>
+      </c>
+      <c r="J28" t="n">
+        <v>16747.33</v>
+      </c>
+      <c r="K28" t="n">
+        <v>7.86</v>
       </c>
     </row>
     <row r="29">
@@ -1850,28 +1944,34 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3123.7</v>
+        <v>3784.61</v>
       </c>
       <c r="C29" t="n">
-        <v>550819</v>
+        <v>784266</v>
       </c>
       <c r="D29" t="n">
-        <v>196498</v>
+        <v>147989</v>
       </c>
       <c r="E29" t="n">
-        <v>8902</v>
+        <v>8569</v>
       </c>
       <c r="F29" t="n">
-        <v>114</v>
+        <v>67</v>
       </c>
       <c r="G29" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="H29" t="n">
-        <v>5.6</v>
+        <v>28</v>
       </c>
       <c r="I29" t="n">
-        <v>16.4</v>
+        <v>11</v>
+      </c>
+      <c r="J29" t="n">
+        <v>20045.61</v>
+      </c>
+      <c r="K29" t="n">
+        <v>7.34</v>
       </c>
     </row>
     <row r="30">
@@ -1881,28 +1981,34 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3944.72</v>
+        <v>3067.64</v>
       </c>
       <c r="C30" t="n">
-        <v>838784</v>
+        <v>766248</v>
       </c>
       <c r="D30" t="n">
-        <v>152899</v>
+        <v>150500</v>
       </c>
       <c r="E30" t="n">
-        <v>6496</v>
+        <v>7522</v>
       </c>
       <c r="F30" t="n">
-        <v>111</v>
+        <v>68</v>
       </c>
       <c r="G30" t="n">
-        <v>93</v>
+        <v>58</v>
       </c>
       <c r="H30" t="n">
-        <v>7.1</v>
+        <v>17</v>
       </c>
       <c r="I30" t="n">
-        <v>12.7</v>
+        <v>10</v>
+      </c>
+      <c r="J30" t="n">
+        <v>13918.19</v>
+      </c>
+      <c r="K30" t="n">
+        <v>7.51</v>
       </c>
     </row>
     <row r="31">
@@ -1912,28 +2018,34 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3125.7</v>
+        <v>3218.57</v>
       </c>
       <c r="C31" t="n">
-        <v>781168</v>
+        <v>811699</v>
       </c>
       <c r="D31" t="n">
-        <v>198800</v>
+        <v>145209</v>
       </c>
       <c r="E31" t="n">
-        <v>7148</v>
+        <v>11073</v>
       </c>
       <c r="F31" t="n">
-        <v>114</v>
+        <v>70</v>
       </c>
       <c r="G31" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="H31" t="n">
-        <v>4.75</v>
+        <v>28</v>
       </c>
       <c r="I31" t="n">
-        <v>13.5</v>
+        <v>13</v>
+      </c>
+      <c r="J31" t="n">
+        <v>20364.52</v>
+      </c>
+      <c r="K31" t="n">
+        <v>7.71</v>
       </c>
     </row>
     <row r="32">
@@ -1943,28 +2055,34 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4369.55</v>
+        <v>3147.24</v>
       </c>
       <c r="C32" t="n">
-        <v>732328</v>
+        <v>875490</v>
       </c>
       <c r="D32" t="n">
-        <v>212132</v>
+        <v>181180</v>
       </c>
       <c r="E32" t="n">
-        <v>6802</v>
+        <v>7955</v>
       </c>
       <c r="F32" t="n">
-        <v>66</v>
+        <v>93</v>
       </c>
       <c r="G32" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="H32" t="n">
-        <v>7.26</v>
+        <v>14</v>
       </c>
       <c r="I32" t="n">
-        <v>17.8</v>
+        <v>14</v>
+      </c>
+      <c r="J32" t="n">
+        <v>22328.01</v>
+      </c>
+      <c r="K32" t="n">
+        <v>5.56</v>
       </c>
     </row>
   </sheetData>
@@ -1988,7 +2106,7 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
   </cols>
@@ -2031,12 +2149,12 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Leads</t>
+          <t>CRM Leads</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Purchases</t>
+          <t>Conversions</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
